--- a/suivi_demarchage_marques.xlsx
+++ b/suivi_demarchage_marques.xlsx
@@ -817,7 +817,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Relance envoyée le 2026-08-10 (Seconde Française 19.24), aucune réponse depuis le 6 août</t>
+          <t>Adrien Degeorges (General Manager) a répondu, créneaux d'appel proposés le 26/08</t>
         </is>
       </c>
     </row>

--- a/suivi_demarchage_marques.xlsx
+++ b/suivi_demarchage_marques.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Légende" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Montres'!$A$1:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Montres'!$A$1:$I$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mode homme'!$A$1:$I$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Maroquinerie'!$A$1:$I$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Parfum dupe'!$A$1:$I$4</definedName>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -634,7 +634,7 @@
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>Collab en attente : montre test = dotation, envoi à confirmer</t>
+          <t>Relance envoyée le 26/08, aucune réponse depuis le 6 août (Jennifer en congés)</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Adrien Degeorges (General Manager) a répondu, créneaux d'appel proposés le 26/08</t>
+          <t>Proposé un échange par écrit plutôt qu'un appel ; modalités test = contrepartie envoyées, en attente de retour</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1165,57 @@
         </is>
       </c>
     </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Baltic</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>support@baltic-watches.com</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>Montre achetée par mes soins (Hermétique) — proposé contrepartie pour un review détaillé</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I13"/>
+  <autoFilter ref="A1:I14"/>
   <dataValidations count="1">
-    <dataValidation sqref="D2:D13 E2:E13 F2:F13 G2:G13 H2:H13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D2:D14 E2:E14 F2:F14 G2:G14 H2:H14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"☑,☐"</formula1>
     </dataValidation>
   </dataValidations>

--- a/suivi_demarchage_marques.xlsx
+++ b/suivi_demarchage_marques.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Montres'!$A$1:$I$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mode homme'!$A$1:$I$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mode homme'!$A$1:$I$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Maroquinerie'!$A$1:$I$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Parfum dupe'!$A$1:$I$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Accessoires tech'!$A$1:$I$2</definedName>
@@ -1229,7 +1229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1430,10 +1430,57 @@
         </is>
       </c>
     </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Le Vent à la Française</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>contact@leventalafrancaise.com</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Brouillon = transfert de notre article de présentation + demande d'échantillon pour un article test dédié — non envoyé</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I4"/>
+  <autoFilter ref="A1:I5"/>
   <dataValidations count="1">
-    <dataValidation sqref="D2:D4 E2:E4 F2:F4 G2:G4 H2:H4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D2:D5 E2:E5 F2:F5 G2:G5 H2:H5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"☑,☐"</formula1>
     </dataValidation>
   </dataValidations>

--- a/suivi_demarchage_marques.xlsx
+++ b/suivi_demarchage_marques.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Légende" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Montres'!$A$1:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Montres'!$A$1:$I$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mode homme'!$A$1:$I$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Maroquinerie'!$A$1:$I$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Parfum dupe'!$A$1:$I$4</definedName>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1212,10 +1212,57 @@
         </is>
       </c>
     </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Triwa</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>info@triwa.com</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Brouillon prêt, non envoyé — pas de presse dédiée, contact général utilisé</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I14"/>
+  <autoFilter ref="A1:I15"/>
   <dataValidations count="1">
-    <dataValidation sqref="D2:D14 E2:E14 F2:F14 G2:G14 H2:H14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D2:D15 E2:E15 F2:F15 G2:G15 H2:H15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"☑,☐"</formula1>
     </dataValidation>
   </dataValidations>

--- a/suivi_demarchage_marques.xlsx
+++ b/suivi_demarchage_marques.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Collab en attente, reprise de contact début septembre</t>
+          <t>Relance début septembre envoyée (brouillon) — calage des modalités : échantillon presse Granvelle contre article détaillé, pas de rémunération</t>
         </is>
       </c>
     </row>
